--- a/request_forms/005_luggage_size_and_dimensions_inquiry_form--request_forms.xlsx
+++ b/request_forms/005_luggage_size_and_dimensions_inquiry_form--request_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -876,8 +876,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="39" customWidth="1" min="2" max="2"/>
-    <col width="39" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -905,12 +905,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'hand_luggage'}</t>
+          <t>hand_luggage</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Hand Luggage'}</t>
+          <t>Hand Luggage</t>
         </is>
       </c>
     </row>
@@ -922,12 +922,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'check-in_luggage'}</t>
+          <t>check-in_luggage</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Check-in Luggage'}</t>
+          <t>Check-in Luggage</t>
         </is>
       </c>
     </row>
@@ -939,12 +939,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'special_luggage'}</t>
+          <t>special_luggage</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Special Luggage'}</t>
+          <t>Special Luggage</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'address_1'}</t>
+          <t>address_1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Address 1'}</t>
+          <t>Address 1</t>
         </is>
       </c>
     </row>
@@ -973,12 +973,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'address_2'}</t>
+          <t>address_2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Address 2'}</t>
+          <t>Address 2</t>
         </is>
       </c>
     </row>
@@ -990,12 +990,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'address_3'}</t>
+          <t>address_3</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Address 3'}</t>
+          <t>Address 3</t>
         </is>
       </c>
     </row>
@@ -1007,12 +1007,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'city_1'}</t>
+          <t>city_1</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'City 1'}</t>
+          <t>City 1</t>
         </is>
       </c>
     </row>
@@ -1024,12 +1024,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'city_2'}</t>
+          <t>city_2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'City 2'}</t>
+          <t>City 2</t>
         </is>
       </c>
     </row>
@@ -1041,12 +1041,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'city_3'}</t>
+          <t>city_3</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'City 3'}</t>
+          <t>City 3</t>
         </is>
       </c>
     </row>
@@ -1058,12 +1058,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'state_1'}</t>
+          <t>state_1</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'State 1'}</t>
+          <t>State 1</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'state_2'}</t>
+          <t>state_2</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'State 2'}</t>
+          <t>State 2</t>
         </is>
       </c>
     </row>
@@ -1092,12 +1092,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'state_3'}</t>
+          <t>state_3</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'State 3'}</t>
+          <t>State 3</t>
         </is>
       </c>
     </row>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'zip_1'}</t>
+          <t>zip_1</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Zip 1'}</t>
+          <t>Zip 1</t>
         </is>
       </c>
     </row>
@@ -1126,12 +1126,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'zip_2'}</t>
+          <t>zip_2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Zip 2'}</t>
+          <t>Zip 2</t>
         </is>
       </c>
     </row>
@@ -1143,12 +1143,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'zip_3'}</t>
+          <t>zip_3</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Zip 3'}</t>
+          <t>Zip 3</t>
         </is>
       </c>
     </row>
